--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1D1393-4886-2F4A-AD29-A908030CC1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0812075E-6C53-EA40-AD65-77D2C825F558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -1260,12 +1260,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1334,6 +1331,12 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1346,9 +1349,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1375,9 +1375,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1497,6 +1494,9 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2537,15 +2537,15 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2563,21 +2563,21 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="24" t="s">
+      <c r="N5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16" t="s">
+      <c r="N6" s="15"/>
+      <c r="O6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2586,13 +2586,13 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="15">
         <v>236</v>
       </c>
     </row>
@@ -2601,13 +2601,13 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="O8" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="15">
         <v>231</v>
       </c>
     </row>
@@ -2618,13 +2618,13 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="15">
         <v>231</v>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="23" t="s">
         <v>85</v>
       </c>
       <c r="C11" s="1"/>
@@ -2679,377 +2679,375 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="49"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="48"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="I6" s="43" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="I6" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="Q6" s="43" t="s">
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="Q6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
       <c r="I8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q8" s="60" t="s">
+      <c r="Q8" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="R8" s="60"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="23">
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="I9" s="27"/>
-      <c r="Q9" s="60" t="s">
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="I9" s="24"/>
+      <c r="Q9" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="23">
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="I10" s="51" t="s">
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="I10" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="53"/>
-      <c r="Q10" s="60" t="s">
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="51"/>
+      <c r="Q10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="60" t="s">
+      <c r="R10" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="60"/>
-      <c r="T10" s="23">
+      <c r="S10" s="43"/>
+      <c r="T10" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="56"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="56"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="54"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="56"/>
-      <c r="Q13" s="43" t="s">
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="Q13" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="41"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="56"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="54"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="I15" s="54"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="56"/>
-      <c r="Q15" s="21" t="s">
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="54"/>
+      <c r="Q15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="R15" s="61" t="s">
+      <c r="R15" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="61"/>
-      <c r="T15" s="61"/>
+      <c r="S15" s="58"/>
+      <c r="T15" s="58"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.2">
-      <c r="I16" s="54"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="56"/>
-      <c r="Q16" s="24" t="s">
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="Q16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="R16" s="30" t="s">
+      <c r="R16" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
     </row>
     <row r="17" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="56"/>
-      <c r="Q17" s="24" t="s">
+      <c r="I17" s="52"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="54"/>
+      <c r="Q17" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="R17" s="30" t="s">
+      <c r="R17" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
     </row>
     <row r="18" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I18" s="54"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="56"/>
-      <c r="Q18" s="24" t="s">
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="54"/>
+      <c r="Q18" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="30" t="s">
+      <c r="R18" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
     </row>
     <row r="19" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I19" s="54"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="56"/>
-      <c r="Q19" s="24" t="s">
+      <c r="I19" s="52"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="54"/>
+      <c r="Q19" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="R19" s="30" t="s">
+      <c r="R19" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
     </row>
     <row r="20" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I20" s="54"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="56"/>
-      <c r="Q20" s="24" t="s">
+      <c r="I20" s="52"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="54"/>
+      <c r="Q20" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="R20" s="30" t="s">
+      <c r="R20" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I21" s="54"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="56"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="46" t="s">
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="54"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="56"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="54"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I23" s="54"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="56"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="30"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="54"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="27"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="I24" s="57"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="59"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="30"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="57"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="27"/>
     </row>
     <row r="25" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="Q25" s="29"/>
-      <c r="R25" s="30"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="27"/>
     </row>
     <row r="26" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="Q26" s="29"/>
-      <c r="R26" s="30"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="27"/>
     </row>
     <row r="27" spans="9:20" x14ac:dyDescent="0.2">
-      <c r="Q27" s="29"/>
-      <c r="R27" s="30"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R21:T21"/>
     <mergeCell ref="B3:K3"/>
@@ -3067,6 +3065,8 @@
     <mergeCell ref="Q9:S9"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3106,476 +3106,476 @@
   <sheetData>
     <row r="1" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="49"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="2:26" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="66"/>
-      <c r="U6" s="66"/>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="66"/>
-      <c r="Y6" s="66"/>
-      <c r="Z6" s="67"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="63"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="63"/>
+      <c r="W6" s="63"/>
+      <c r="X6" s="63"/>
+      <c r="Y6" s="63"/>
+      <c r="Z6" s="64"/>
     </row>
     <row r="7" spans="2:26" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="72" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="69" t="s">
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="68" t="s">
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="U7" s="66"/>
-      <c r="V7" s="66"/>
-      <c r="W7" s="66"/>
-      <c r="X7" s="66"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="67"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="63"/>
+      <c r="Y7" s="63"/>
+      <c r="Z7" s="64"/>
     </row>
     <row r="8" spans="2:26" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="64"/>
-      <c r="C8" s="70" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="71" t="s">
+      <c r="E8" s="61"/>
+      <c r="F8" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="71" t="s">
+      <c r="G8" s="64"/>
+      <c r="H8" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="67"/>
-      <c r="J8" s="71" t="s">
+      <c r="I8" s="64"/>
+      <c r="J8" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K8" s="67"/>
-      <c r="L8" s="71" t="s">
+      <c r="K8" s="64"/>
+      <c r="L8" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="M8" s="67"/>
-      <c r="N8" s="69" t="s">
+      <c r="M8" s="64"/>
+      <c r="N8" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="69" t="s">
+      <c r="O8" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="P8" s="69" t="s">
+      <c r="P8" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="69" t="s">
+      <c r="Q8" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="69" t="s">
+      <c r="R8" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S8" s="69" t="s">
+      <c r="S8" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="T8" s="68">
+      <c r="T8" s="65">
         <v>0</v>
       </c>
-      <c r="U8" s="68">
+      <c r="U8" s="65">
         <v>1</v>
       </c>
-      <c r="V8" s="68">
+      <c r="V8" s="65">
         <v>2</v>
       </c>
-      <c r="W8" s="68" t="s">
+      <c r="W8" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="X8" s="68" t="s">
+      <c r="X8" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="Y8" s="68" t="s">
+      <c r="Y8" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="Z8" s="68" t="s">
+      <c r="Z8" s="65" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="32" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="65"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="65"/>
-      <c r="Z9" s="65"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="62"/>
     </row>
     <row r="10" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36" t="s">
+      <c r="F10" s="33"/>
+      <c r="G10" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="37" t="s">
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
     </row>
     <row r="11" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36" t="s">
+      <c r="G11" s="33"/>
+      <c r="H11" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37" t="s">
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
     </row>
     <row r="12" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37" t="s">
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="38" t="s">
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
     </row>
     <row r="13" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36" t="s">
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="36" t="s">
+      <c r="J13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36" t="s">
+      <c r="L13" s="33"/>
+      <c r="M13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37" t="s">
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38" t="s">
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
     </row>
     <row r="14" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36" t="s">
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="36" t="s">
+      <c r="J14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="L14" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M14" s="36"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37" t="s">
+      <c r="M14" s="33"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38" t="s">
+      <c r="S14" s="34"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
     </row>
     <row r="15" spans="2:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36" t="s">
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
-      <c r="S15" s="37" t="s">
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38" t="s">
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="38"/>
-      <c r="Z15" s="38"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
     </row>
     <row r="16" spans="2:26" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="9"/>
@@ -3637,46 +3637,46 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B1" s="8"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="80"/>
-      <c r="G4" s="76" t="s">
+      <c r="F4" s="77"/>
+      <c r="G4" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="77"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="75"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="84"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="81"/>
       <c r="E5" s="2" t="s">
         <v>94</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="B6" s="10">
         <v>9</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="75" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3706,10 +3706,10 @@
       <c r="F6" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="31" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       <c r="B7" s="10">
         <v>10</v>
       </c>
-      <c r="C7" s="78"/>
+      <c r="C7" s="75"/>
       <c r="D7" s="4" t="s">
         <v>61</v>
       </c>
@@ -3727,10 +3727,10 @@
       <c r="F7" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="31" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       <c r="B8" s="10">
         <v>11</v>
       </c>
-      <c r="C8" s="78"/>
+      <c r="C8" s="75"/>
       <c r="D8" s="4" t="s">
         <v>102</v>
       </c>
@@ -3748,10 +3748,10 @@
       <c r="F8" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="37" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       <c r="B9" s="10">
         <v>12</v>
       </c>
-      <c r="C9" s="78"/>
+      <c r="C9" s="75"/>
       <c r="D9" s="4" t="s">
         <v>106</v>
       </c>
@@ -3769,18 +3769,18 @@
       <c r="F9" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="H9" s="31" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="41">
+      <c r="B10" s="38">
         <v>13</v>
       </c>
-      <c r="C10" s="78"/>
+      <c r="C10" s="75"/>
       <c r="D10" s="4" t="s">
         <v>109</v>
       </c>
@@ -3790,10 +3790,10 @@
       <c r="F10" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="H10" s="31" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       <c r="B11" s="2">
         <v>14</v>
       </c>
-      <c r="C11" s="79"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="4" t="s">
         <v>113</v>
       </c>
@@ -3811,16 +3811,16 @@
       <c r="F11" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="31" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
-      <c r="C12" s="42"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -3843,64 +3843,64 @@
       <c r="G14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="31" t="s">
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="101"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="89" t="s">
+      <c r="G15" s="98"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="90"/>
+      <c r="J15" s="87"/>
     </row>
     <row r="16" spans="2:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="92" t="s">
+      <c r="D16" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="94" t="s">
+      <c r="E16" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="96" t="s">
+      <c r="F16" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="85" t="s">
+      <c r="H16" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="87" t="s">
+      <c r="I16" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="81" t="s">
+      <c r="J16" s="78" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="91"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="96"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="93"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <f>SUM(C18:D18)</f>
         <v>6</v>
       </c>
@@ -3910,20 +3910,24 @@
       <c r="D18" s="13">
         <v>0</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15" t="s">
+      <c r="E18" s="100">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="17">
-        <v>0</v>
-      </c>
-      <c r="H18" s="18"/>
       <c r="I18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="19">
-        <f>C18</f>
-        <v>6</v>
+      <c r="J18" s="102" t="e">
+        <f>-H18</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -3956,17 +3960,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3975,7 +3968,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="08d9df77a39a0ee87f79f9436c57bbce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" xmlns:ns3="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="03dd79bc1474883a2d909db85c328b07" ns2:_="" ns3:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4164,18 +4157,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4183,7 +4176,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B359A3C-84EA-4FDD-BB5C-023A91F35CC6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4200,4 +4193,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>